--- a/survey_templates/032_food_quality_assessment_quiz--survey_templates.xlsx
+++ b/survey_templates/032_food_quality_assessment_quiz--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'how_would_you_rate_the_food_quality_of_this_establishment?',_'value':_1}</t>
+          <t>how_would_you_rate_the_food_quality_of_this_establishment?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'How would you rate the food quality of this establishment?', 'value': 1}</t>
+          <t>How would you rate the food quality of this establishment?</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'excellent',_'value':_2}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Excellent', 'value': 2}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'very_good',_'value':_3}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Very good', 'value': 3}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'average',_'value':_4}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Average', 'value': 4}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'poor',_'value':_5}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Poor', 'value': 5}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent',_'value':_1}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent', 'value': 1}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'very_good',_'value':_2}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Very good', 'value': 2}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'average',_'value':_3}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Average', 'value': 3}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'poor',_'value':_4}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Poor', 'value': 4}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
